--- a/data/trending_integrated_20260922_12.xlsx
+++ b/data/trending_integrated_20260922_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51848869140</v>
+        <v>51865962040</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>노타, 국산 NPU 기반 휴머노이드 개발 착수 소식에 대한 기대감 상승. 일부 투자자들은 기술력 기반의 추가 상승을 전망하나, 실적 부재 및 단기 하락 가능성을 경고하는 의견도 존재.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스. AI 반도체 파트너십 및 로봇 속도 초가속 효과 기대. 잭팟 메가톤급 재료 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5390415099</v>
+        <v>5398296919</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65900</v>
+        <v>65800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+26.00%</t>
+          <t>'+25.81%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>147285556500</v>
+        <v>149690544500</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 키맞추기 장세 속 급등. 20일선 안착 여부가 중요.</t>
+          <t>상승세를 이어가며 전고점 돌파 기대감. 브로드컴 투자 공급 계약 언급. 20일선 안착 여부 중요.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '키맞추기', '20일선']</t>
+          <t>['전고점', '브로드컴', '20일선']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13390</v>
+        <v>13340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+20.41%</t>
+          <t>'+19.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>136300367030</v>
+        <v>141669854340</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대미 투자 1호 텍사스 가스발전 사업 확정으로 인한 가스터빈 관련주 부각. 주가 급등세.</t>
+          <t>가스터빈 대장주로 부각. 대미투자 1호 텍사스 가스발전 관련 수혜 기대감. 국회 보고 완료 및 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114600</v>
+        <v>114300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.46%</t>
+          <t>'+12.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
         <v>82</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>269030832600</v>
+        <v>270407457200</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32150</v>
+        <v>32100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.25%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>227775347225</v>
+        <v>229570724050</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 35,000원 목표 제시. AI 전력 수요 폭증 관련 수혜 기대감 있으나, 경쟁 종목 대비 부진.</t>
+          <t>단기 3만 5천원 상승 가능성 언급. AI 전력수요 폭증 관련 수혜 기대감. 목표가 40,000~70,000 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '전력', '신고점']</t>
+          <t>['AI', '전력수요', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6230</v>
+        <v>30700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.31%</t>
+          <t>'+6.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.19</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>127</v>
+        <v>210</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51.96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5860</v>
+        <v>28850</v>
       </c>
       <c r="K8" t="n">
-        <v>6200</v>
+        <v>29250</v>
       </c>
       <c r="L8" t="n">
-        <v>6610</v>
+        <v>30700</v>
       </c>
       <c r="M8" t="n">
-        <v>6150</v>
+        <v>29150</v>
       </c>
       <c r="N8" t="n">
-        <v>0.19</v>
+        <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>59767577645</v>
+        <v>82592487275</v>
       </c>
       <c r="P8" t="n">
-        <v>13140</v>
+        <v>31200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3725</v>
+        <v>21000</v>
       </c>
       <c r="R8" t="n">
-        <v>48000</v>
+        <v>324000</v>
       </c>
       <c r="S8" t="n">
-        <v>27000</v>
+        <v>118000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
+          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['국제유가', '환율', '매수세']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30650</v>
+        <v>6200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.24%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="H9" t="n">
-        <v>51.95</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28850</v>
+        <v>5860</v>
       </c>
       <c r="K9" t="n">
-        <v>29250</v>
+        <v>6200</v>
       </c>
       <c r="L9" t="n">
-        <v>30650</v>
+        <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>29150</v>
+        <v>6150</v>
       </c>
       <c r="N9" t="n">
-        <v>25.79</v>
+        <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>78242666100</v>
+        <v>60866441735</v>
       </c>
       <c r="P9" t="n">
-        <v>31200</v>
+        <v>13140</v>
       </c>
       <c r="Q9" t="n">
-        <v>21000</v>
+        <v>3725</v>
       </c>
       <c r="R9" t="n">
-        <v>324000</v>
+        <v>48000</v>
       </c>
       <c r="S9" t="n">
-        <v>118000</v>
+        <v>27000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '환율', '매수세']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
@@ -1317,10 +1317,10 @@
         <v>57</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H10" t="n">
         <v>4.86</v>
@@ -1346,7 +1346,7 @@
         <v>4.95</v>
       </c>
       <c r="O10" t="n">
-        <v>48917192825</v>
+        <v>49022711750</v>
       </c>
       <c r="P10" t="n">
         <v>11760</v>
@@ -1406,13 +1406,13 @@
         <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H11" t="n">
         <v>3.22</v>
@@ -1438,7 +1438,7 @@
         <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>104689959500</v>
+        <v>105480950500</v>
       </c>
       <c r="P11" t="n">
         <v>635000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신고가 돌파 후 추가 상승 기대감. 구리 가격 상승 및 모더나 관련 모멘텀.</t>
+          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신고가', '구리', '성장동력']</t>
+          <t>['신고가', '테마주', '외인지분율']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>-0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H12" t="n">
         <v>3.34</v>
@@ -1530,7 +1530,7 @@
         <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>86561837280</v>
+        <v>86911140445</v>
       </c>
       <c r="P12" t="n">
         <v>20300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13350</v>
+        <v>18820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+2.90%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>298</v>
+        <v>539</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>18290</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>18830</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>19540</v>
       </c>
       <c r="M13" t="n">
-        <v>13250</v>
+        <v>18540</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>19513562730</v>
+        <v>106149876260</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-41000</v>
+        <v>-76000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>공매도 관련 이슈 부각되며 주가 상승 기대감 형성. 대미 원전 및 LNG 사업 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['공매도', '원전', 'LNG']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18820</v>
+        <v>213500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.90%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>541</v>
+        <v>216</v>
       </c>
       <c r="H14" t="n">
-        <v>10.47</v>
+        <v>75.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18290</v>
+        <v>208000</v>
       </c>
       <c r="K14" t="n">
-        <v>18830</v>
+        <v>215000</v>
       </c>
       <c r="L14" t="n">
-        <v>19540</v>
+        <v>215000</v>
       </c>
       <c r="M14" t="n">
-        <v>18540</v>
+        <v>211000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>104646989050</v>
+        <v>520113104750</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>64700</v>
       </c>
       <c r="R14" t="n">
-        <v>-76000</v>
+        <v>-691000</v>
       </c>
       <c r="S14" t="n">
-        <v>9000</v>
+        <v>13000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 관련 이슈 부각되며 주가 상승 기대감 형성. 대미 원전 및 LNG 사업 기대감.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '원전', 'LNG']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214000</v>
+        <v>1917000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>476</v>
       </c>
       <c r="G15" t="n">
-        <v>211</v>
+        <v>2572</v>
       </c>
       <c r="H15" t="n">
-        <v>75.5</v>
+        <v>50.17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>208000</v>
+        <v>1868000</v>
       </c>
       <c r="K15" t="n">
-        <v>215000</v>
+        <v>1909000</v>
       </c>
       <c r="L15" t="n">
-        <v>215000</v>
+        <v>1935000</v>
       </c>
       <c r="M15" t="n">
-        <v>211000</v>
+        <v>1904000</v>
       </c>
       <c r="N15" t="n">
-        <v>75.44</v>
+        <v>50.23</v>
       </c>
       <c r="O15" t="n">
-        <v>499177480500</v>
+        <v>2637074684500</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>64700</v>
+        <v>333000</v>
       </c>
       <c r="R15" t="n">
-        <v>-691000</v>
+        <v>82000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>44000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>반도체 업황 회복 및 AI 관련주 강세. 인텔, AMD, 메타 동반 상승 기대감. 자사주 매수 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['반도체', 'AI', '자사주매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1920000</v>
+        <v>13300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>477</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>2664</v>
+        <v>301</v>
       </c>
       <c r="H16" t="n">
-        <v>50.17</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1868000</v>
+        <v>12960</v>
       </c>
       <c r="K16" t="n">
-        <v>1909000</v>
+        <v>13500</v>
       </c>
       <c r="L16" t="n">
-        <v>1935000</v>
+        <v>14190</v>
       </c>
       <c r="M16" t="n">
-        <v>1904000</v>
+        <v>13250</v>
       </c>
       <c r="N16" t="n">
-        <v>50.23</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2566222055000</v>
+        <v>19626140740</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>333000</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>82000</v>
+        <v>-41000</v>
       </c>
       <c r="S16" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 주 강세 및 미국 반도체주 폭등에 따른 동반 상승 기대. 230-240까지 상승 전망.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '상승']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="G17" t="n">
-        <v>2096</v>
+        <v>2035</v>
       </c>
       <c r="H17" t="n">
         <v>46.56</v>
@@ -1990,7 +1990,7 @@
         <v>46.46</v>
       </c>
       <c r="O17" t="n">
-        <v>2114268661000</v>
+        <v>2221157581000</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 낙관론 및 배당 기대감 속 주가 상승 전망. HBM 1위 기업으로서 목표가 56만원 제시.</t>
+          <t>AI 낙관론에 따른 주가 상승 기대감 존재. 배당금 및 특별배당 기대감으로 주가 상승 전망. 월가 목표가 56만원 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '배당', 'HBM']</t>
+          <t>['AI', '배당금', '목표가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17950</v>
+        <v>21800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+1.40%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.68</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>665</v>
+        <v>191</v>
       </c>
       <c r="H18" t="n">
-        <v>6.22</v>
+        <v>1.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,419 +2067,419 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17720</v>
+        <v>21500</v>
       </c>
       <c r="K18" t="n">
-        <v>18230</v>
+        <v>21200</v>
       </c>
       <c r="L18" t="n">
-        <v>18750</v>
+        <v>22900</v>
       </c>
       <c r="M18" t="n">
-        <v>17500</v>
+        <v>20850</v>
       </c>
       <c r="N18" t="n">
-        <v>7.9</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>133520576030</v>
+        <v>45512668100</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>22900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>9900</v>
       </c>
       <c r="R18" t="n">
-        <v>-545000</v>
+        <v>47000</v>
       </c>
       <c r="S18" t="n">
-        <v>7000</v>
+        <v>-3000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 동반 상승 기대감. 메타발 광케이블 사업 수혜 전망.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '메타', '광케이블']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10640</v>
+        <v>86000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.85%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>312</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G19" t="n">
-        <v>162</v>
+        <v>1107</v>
       </c>
       <c r="H19" t="n">
-        <v>9.609999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10550</v>
+        <v>85300</v>
       </c>
       <c r="K19" t="n">
-        <v>10730</v>
+        <v>87000</v>
       </c>
       <c r="L19" t="n">
-        <v>11160</v>
+        <v>87000</v>
       </c>
       <c r="M19" t="n">
-        <v>10300</v>
+        <v>85200</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>23.12</v>
       </c>
       <c r="O19" t="n">
-        <v>116628438095</v>
+        <v>114264326900</v>
       </c>
       <c r="P19" t="n">
-        <v>11640</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3735</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>209000</v>
+        <v>-200000</v>
       </c>
       <c r="S19" t="n">
-        <v>-38000</v>
+        <v>-4000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>대미 투자 SMR 추진 확정 및 가스터빈 관련주 부각. 주가 급등세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '가스터빈', '대미투자']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85900</v>
+        <v>10590</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>1095</v>
+        <v>162</v>
       </c>
       <c r="H20" t="n">
-        <v>23.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>85300</v>
+        <v>10550</v>
       </c>
       <c r="K20" t="n">
-        <v>87000</v>
+        <v>10730</v>
       </c>
       <c r="L20" t="n">
-        <v>87000</v>
+        <v>11160</v>
       </c>
       <c r="M20" t="n">
-        <v>85200</v>
+        <v>10300</v>
       </c>
       <c r="N20" t="n">
-        <v>23.12</v>
+        <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>112165725500</v>
+        <v>117815119590</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>11640</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>3735</v>
       </c>
       <c r="R20" t="n">
-        <v>-200000</v>
+        <v>209000</v>
       </c>
       <c r="S20" t="n">
-        <v>-4000</v>
+        <v>-38000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대미 투자 SMR 추진 확정 및 가스터빈 관련주 부각. 주가 급등세.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '대미투자']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21650</v>
+        <v>8530</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>187</v>
+        <v>313</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>26.58</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>21500</v>
+        <v>8520</v>
       </c>
       <c r="K21" t="n">
-        <v>21200</v>
+        <v>8620</v>
       </c>
       <c r="L21" t="n">
-        <v>22900</v>
+        <v>8650</v>
       </c>
       <c r="M21" t="n">
-        <v>20850</v>
+        <v>8410</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>44246016100</v>
+        <v>15765631660</v>
       </c>
       <c r="P21" t="n">
-        <v>22900</v>
+        <v>17950</v>
       </c>
       <c r="Q21" t="n">
-        <v>9900</v>
+        <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>47000</v>
+        <v>-418000</v>
       </c>
       <c r="S21" t="n">
-        <v>-3000</v>
+        <v>18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>실적 부진 및 무능함 지적. 10배 수익 가능성 언급과 상반된 부정적 전망 혼재. 대차잔고 감소는 긍정적 요인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['적자', '실적', '대차잔고']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8540</v>
+        <v>17900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'-2.72%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>306</v>
+        <v>678</v>
       </c>
       <c r="H22" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8520</v>
+        <v>18400</v>
       </c>
       <c r="K22" t="n">
-        <v>8620</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8650</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>8410</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O22" t="n">
-        <v>15415658850</v>
+        <v>137465000000</v>
       </c>
       <c r="P22" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-418000</v>
+        <v>-545000</v>
       </c>
       <c r="S22" t="n">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>적자 회사로 인한 가치 판단 흐림. 주가 부양 노력에도 불구하고 장기 소외 및 비전 부재.</t>
+          <t>미국 광통신 업황 호조에 따른 동반 상승 기대감. 메타발 광케이블 관련 기대감 언급. 900억 투자 주의 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['적자', '장기소외', '가치평가']</t>
+          <t>['광케이블', '메타', '투자주의']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24350</v>
+        <v>24200</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
         <v>186</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>94043223250</v>
+        <v>94477933575</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>삼성과의 협업 기대감 및 코스닥 역사적 종목 성장 전망.</t>
+          <t>단기 상승 후 하락세 전환 가능성 언급. 협업 및 재무 상태에 대한 불확실성 존재. 프로그램 매집에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['삼성', '협업', '코스닥']</t>
+          <t>['협업', '재무', '프로그램매집']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3885</v>
+        <v>3865</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.19%</t>
+          <t>'-4.69%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>9606974252</v>
+        <v>9767276987</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10520</v>
+        <v>10390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-6.06%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G25" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>35123010865</v>
+        <v>35488485090</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_12.xlsx
+++ b/data/trending_integrated_20260922_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F2" t="n">
         <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51865962040</v>
+        <v>51916992690</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스. AI 반도체 파트너십 및 로봇 속도 초가속 효과 기대. 잭팟 메가톤급 재료 언급.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스에 따른 기대감 고조. 다만, 실적 부재 및 주가 하락 우려도 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5398296919</v>
+        <v>5402185899</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65800</v>
+        <v>65300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.81%</t>
+          <t>'+24.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>149690544500</v>
+        <v>153010648150</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상승세를 이어가며 전고점 돌파 기대감. 브로드컴 투자 공급 계약 언급. 20일선 안착 여부 중요.</t>
+          <t>브로드컴 공급 계약 뉴스에 따른 급등세. 고점 매도 의견과 추가 상승 기대 상존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전고점', '브로드컴', '20일선']</t>
+          <t>['브로드컴', '공급계약', '키맞추기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13340</v>
+        <v>13140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+19.96%</t>
+          <t>'+18.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>141669854340</v>
+        <v>146032917245</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가스터빈 대장주로 부각. 대미투자 1호 텍사스 가스발전 관련 수혜 기대감. 국회 보고 완료 및 관련 뉴스 언급.</t>
+          <t>대미 투자 1호 가스발전 사업 관련 보도에 대한 기대와 회의론 혼재. 급락 및 탈출 의견 다수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '대미투자', '가스발전']</t>
+          <t>['대미투자', '가스터빈', '개잡주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114300</v>
+        <v>115600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.17%</t>
+          <t>'+13.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,7 +949,7 @@
         <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
         <v>82</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>270407457200</v>
+        <v>272880681600</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32100</v>
+        <v>32275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>229570724050</v>
+        <v>231141831425</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 3만 5천원 상승 가능성 언급. AI 전력수요 폭증 관련 수혜 기대감. 목표가 40,000~70,000 제시.</t>
+          <t>AI 전력수요 증가에 따른 기대감 속 단기 급등 가능성 언급. 그러나 신고점 돌파 실패 및 하락세 관측 상존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '전력수요', '목표가']</t>
+          <t>['AI', '전력수요', '신고점']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30700</v>
+        <v>30725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.41%</t>
+          <t>'+6.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="H8" t="n">
-        <v>51.96</v>
+        <v>51.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>29250</v>
       </c>
       <c r="L8" t="n">
-        <v>30700</v>
+        <v>30750</v>
       </c>
       <c r="M8" t="n">
         <v>29150</v>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>82592487275</v>
+        <v>84540964300</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1222,10 +1222,10 @@
         <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
         <v>126</v>
@@ -1254,7 +1254,7 @@
         <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>60866441735</v>
+        <v>61269170225</v>
       </c>
       <c r="P9" t="n">
         <v>13140</v>
@@ -1314,13 +1314,13 @@
         <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H10" t="n">
         <v>4.86</v>
@@ -1346,7 +1346,7 @@
         <v>4.95</v>
       </c>
       <c r="O10" t="n">
-        <v>49022711750</v>
+        <v>49209389790</v>
       </c>
       <c r="P10" t="n">
         <v>11760</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>329500</v>
+        <v>330500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.45%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H11" t="n">
         <v>3.22</v>
@@ -1438,7 +1438,7 @@
         <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>105480950500</v>
+        <v>106377869250</v>
       </c>
       <c r="P11" t="n">
         <v>635000</v>
@@ -1498,13 +1498,13 @@
         <v>-0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H12" t="n">
         <v>3.34</v>
@@ -1530,7 +1530,7 @@
         <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>86911140445</v>
+        <v>87302460805</v>
       </c>
       <c r="P12" t="n">
         <v>20300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18820</v>
+        <v>18810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.90%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="H13" t="n">
         <v>10.47</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>106149876260</v>
+        <v>107137042180</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 관련 이슈 부각되며 주가 상승 기대감 형성. 대미 원전 및 LNG 사업 기대감.</t>
+          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '원전', 'LNG']</t>
+          <t>['공매도', '대차', 'LNG']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1688,7 +1688,7 @@
         <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="H14" t="n">
         <v>75.5</v>
@@ -1714,7 +1714,7 @@
         <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>520113104750</v>
+        <v>529296318750</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1917000</v>
+        <v>1916000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G15" t="n">
-        <v>2572</v>
+        <v>2394</v>
       </c>
       <c r="H15" t="n">
         <v>50.17</v>
@@ -1806,7 +1806,7 @@
         <v>50.23</v>
       </c>
       <c r="O15" t="n">
-        <v>2637074684500</v>
+        <v>2699607848500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 업황 회복 및 AI 관련주 강세. 인텔, AMD, 메타 동반 상승 기대감. 자사주 매수 시작 가능성 언급.</t>
+          <t>AI 개발 경쟁 심화 및 앤트로픽 신규 모델 출시 검토 소식에 따른 상승 기대. 200만원 돌파 및 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '자사주매수']</t>
+          <t>['AI', '앤트로픽', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13300</v>
+        <v>281000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>497</v>
       </c>
       <c r="G16" t="n">
-        <v>301</v>
+        <v>2079</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12960</v>
+        <v>274000</v>
       </c>
       <c r="K16" t="n">
-        <v>13500</v>
+        <v>283000</v>
       </c>
       <c r="L16" t="n">
-        <v>14190</v>
+        <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>13250</v>
+        <v>278500</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>19626140740</v>
+        <v>2289893383750</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>-41000</v>
+        <v>-116000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>128000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 낙관론과 배당 기대감 속에서 30만 돌파 가능성 언급. 다만, 정치적 발언 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI', '배당', 'HBM']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>281000</v>
+        <v>13280</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>499</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>2035</v>
+        <v>313</v>
       </c>
       <c r="H17" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>274000</v>
+        <v>12960</v>
       </c>
       <c r="K17" t="n">
-        <v>283000</v>
+        <v>13500</v>
       </c>
       <c r="L17" t="n">
-        <v>283500</v>
+        <v>14190</v>
       </c>
       <c r="M17" t="n">
-        <v>278500</v>
+        <v>13250</v>
       </c>
       <c r="N17" t="n">
-        <v>46.46</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2221157581000</v>
+        <v>19722898590</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>81100</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-116000</v>
+        <v>-41000</v>
       </c>
       <c r="S17" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감 존재. 배당금 및 특별배당 기대감으로 주가 상승 전망. 월가 목표가 56만원 언급.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '배당금', '목표가']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21800</v>
+        <v>21850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+1.63%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H18" t="n">
         <v>1.2</v>
@@ -2082,7 +2082,7 @@
         <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>45512668100</v>
+        <v>45947383200</v>
       </c>
       <c r="P18" t="n">
         <v>22900</v>
@@ -2127,123 +2127,123 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86000</v>
+        <v>10660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E19" t="n">
-        <v>312</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>1107</v>
+        <v>166</v>
       </c>
       <c r="H19" t="n">
-        <v>23.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>85300</v>
+        <v>10550</v>
       </c>
       <c r="K19" t="n">
-        <v>87000</v>
+        <v>10730</v>
       </c>
       <c r="L19" t="n">
-        <v>87000</v>
+        <v>11160</v>
       </c>
       <c r="M19" t="n">
-        <v>85200</v>
+        <v>10300</v>
       </c>
       <c r="N19" t="n">
-        <v>23.12</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>114264326900</v>
+        <v>119037992815</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>11640</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>3735</v>
       </c>
       <c r="R19" t="n">
-        <v>-200000</v>
+        <v>209000</v>
       </c>
       <c r="S19" t="n">
-        <v>-4000</v>
+        <v>-38000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대미 투자 SMR 추진 확정 및 가스터빈 관련주 부각. 주가 급등세.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '대미투자']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10590</v>
+        <v>17900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="G20" t="n">
-        <v>162</v>
+        <v>694</v>
       </c>
       <c r="H20" t="n">
-        <v>9.609999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10550</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>10730</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>11160</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>10300</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>117815119590</v>
+        <v>138554354545</v>
       </c>
       <c r="P20" t="n">
-        <v>11640</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3735</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>209000</v>
+        <v>-545000</v>
       </c>
       <c r="S20" t="n">
-        <v>-38000</v>
+        <v>7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>미국 광통신 섹터 강세에 따른 기대감. 2만원 돌파 및 급등 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['광통신', '미국', '급등']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8530</v>
+        <v>86000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>313</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="G21" t="n">
-        <v>313</v>
+        <v>1119</v>
       </c>
       <c r="H21" t="n">
-        <v>26.58</v>
+        <v>23.05</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8520</v>
+        <v>85300</v>
       </c>
       <c r="K21" t="n">
-        <v>8620</v>
+        <v>87000</v>
       </c>
       <c r="L21" t="n">
-        <v>8650</v>
+        <v>87000</v>
       </c>
       <c r="M21" t="n">
-        <v>8410</v>
+        <v>85200</v>
       </c>
       <c r="N21" t="n">
-        <v>26.57</v>
+        <v>23.12</v>
       </c>
       <c r="O21" t="n">
-        <v>15765631660</v>
+        <v>116316715150</v>
       </c>
       <c r="P21" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-418000</v>
+        <v>-200000</v>
       </c>
       <c r="S21" t="n">
-        <v>18000</v>
+        <v>-4000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 부진 및 무능함 지적. 10배 수익 가능성 언급과 상반된 부정적 전망 혼재. 대차잔고 감소는 긍정적 요인.</t>
+          <t>미국 SMR 추진 및 가스터빈 사업 관련 확정 소식에 따른 강한 상승 기대감. 10만 돌파 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['적자', '실적', '대차잔고']</t>
+          <t>['SMR', '가스터빈', '대미투자']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,77 +2396,77 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17900</v>
+        <v>8540</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.72%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>678</v>
+        <v>318</v>
       </c>
       <c r="H22" t="n">
-        <v>6.22</v>
+        <v>26.58</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>18400</v>
+        <v>8520</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>8620</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>8650</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>8410</v>
       </c>
       <c r="N22" t="n">
-        <v>7.9</v>
+        <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>137465000000</v>
+        <v>15967936770</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>-545000</v>
+        <v>-418000</v>
       </c>
       <c r="S22" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 광통신 업황 호조에 따른 동반 상승 기대감. 메타발 광케이블 관련 기대감 언급. 900억 투자 주의 언급.</t>
+          <t>반도체 업황 부진 속에서 LG디스플레이의 실적 개선 및 주가 상승에 대한 회의적 시각.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광케이블', '메타', '투자주의']</t>
+          <t>['반도체', '적자', '주가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24200</v>
+        <v>24250</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-3.96%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H23" t="n">
         <v>1.76</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>94477933575</v>
+        <v>94885665750</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>단기 상승 후 하락세 전환 가능성 언급. 협업 및 재무 상태에 대한 불확실성 존재. 프로그램 매집에 대한 의문 제기.</t>
+          <t>미국 임상 FDA 관련 기대감 속에서 단기 급등 후 하락세. 투자자들의 혼란과 탈출 시도.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['협업', '재무', '프로그램매집']</t>
+          <t>['미국임상', 'FDA', '급등']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2602,13 +2602,13 @@
         <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G24" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>9767276987</v>
+        <v>9836390822</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10390</v>
+        <v>10410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>35488485090</v>
+        <v>35775881960</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_12.xlsx
+++ b/data/trending_integrated_20260922_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51916992690</v>
+        <v>51974111840</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5402185899</v>
+        <v>5402814829</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65300</v>
+        <v>65200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.86%</t>
+          <t>'+24.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
         <v>101</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>153010648150</v>
+        <v>155627575250</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13140</v>
+        <v>13180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+18.17%</t>
+          <t>'+18.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>146032917245</v>
+        <v>148973537155</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대미 투자 1호 가스발전 사업 관련 보도에 대한 기대와 회의론 혼재. 급락 및 탈출 의견 다수.</t>
+          <t>대미 투자 1호 가스 발전 관련 뉴스에도 불구하고, 하한가 및 개잡주라는 부정적 평가 우세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115600</v>
+        <v>115200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.44%</t>
+          <t>'+13.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>272880681600</v>
+        <v>274776141800</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32275</v>
+        <v>32300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.67%</t>
+          <t>'+8.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>231141831425</v>
+        <v>231997917825</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 전력수요 증가에 따른 기대감 속 단기 급등 가능성 언급. 그러나 신고점 돌파 실패 및 하락세 관측 상존.</t>
+          <t>가온전선과의 비교 속에서 주가 상승 기대감 있으나, 전고점 돌파 실패 및 외인/기관 매도 시작으로 부정적.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '전력수요', '신고점']</t>
+          <t>['전고점', '외인', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,16 +1130,16 @@
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H8" t="n">
-        <v>51.97</v>
+        <v>51.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>84540964300</v>
+        <v>87066267850</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6200</v>
+        <v>6140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.80%</t>
+          <t>'+4.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>6150</v>
+        <v>6110</v>
       </c>
       <c r="N9" t="n">
         <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>61269170225</v>
+        <v>62855381985</v>
       </c>
       <c r="P9" t="n">
         <v>13140</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
+          <t>비트코인 급등에 따른 코인주 반란 기대감. 업비트 나스닥 상장 및 비트코인 신고가 경신 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['비트코인', '코인주', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6560</v>
+        <v>331000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="H10" t="n">
-        <v>4.86</v>
+        <v>3.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6310</v>
+        <v>318500</v>
       </c>
       <c r="K10" t="n">
-        <v>6460</v>
+        <v>333000</v>
       </c>
       <c r="L10" t="n">
-        <v>7090</v>
+        <v>349500</v>
       </c>
       <c r="M10" t="n">
-        <v>6350</v>
+        <v>325000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.95</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
-        <v>49209389790</v>
+        <v>106696244500</v>
       </c>
       <c r="P10" t="n">
-        <v>11760</v>
+        <v>635000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1620</v>
+        <v>52600</v>
       </c>
       <c r="R10" t="n">
-        <v>-92000</v>
+        <v>-8000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['신고가', '테마주', '외인지분율']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,91 +1379,91 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330500</v>
+        <v>6550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>264</v>
+        <v>153</v>
       </c>
       <c r="H11" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>318500</v>
+        <v>6310</v>
       </c>
       <c r="K11" t="n">
-        <v>333000</v>
+        <v>6460</v>
       </c>
       <c r="L11" t="n">
-        <v>349500</v>
+        <v>7090</v>
       </c>
       <c r="M11" t="n">
-        <v>325000</v>
+        <v>6350</v>
       </c>
       <c r="N11" t="n">
-        <v>3.62</v>
+        <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>106377869250</v>
+        <v>49289308990</v>
       </c>
       <c r="P11" t="n">
-        <v>635000</v>
+        <v>11760</v>
       </c>
       <c r="Q11" t="n">
-        <v>52600</v>
+        <v>1620</v>
       </c>
       <c r="R11" t="n">
-        <v>-8000</v>
+        <v>-92000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신고가', '테마주', '외인지분율']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H12" t="n">
         <v>3.34</v>
@@ -1530,7 +1530,7 @@
         <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>87302460805</v>
+        <v>87548516380</v>
       </c>
       <c r="P12" t="n">
         <v>20300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18810</v>
+        <v>214000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.88%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>556</v>
+        <v>244</v>
       </c>
       <c r="H13" t="n">
-        <v>10.47</v>
+        <v>75.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18290</v>
+        <v>208000</v>
       </c>
       <c r="K13" t="n">
-        <v>18830</v>
+        <v>215000</v>
       </c>
       <c r="L13" t="n">
-        <v>19540</v>
+        <v>215000</v>
       </c>
       <c r="M13" t="n">
-        <v>18540</v>
+        <v>211000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.74</v>
+        <v>75.44</v>
       </c>
       <c r="O13" t="n">
-        <v>107137042180</v>
+        <v>539294732250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>64700</v>
       </c>
       <c r="R13" t="n">
-        <v>-76000</v>
+        <v>-691000</v>
       </c>
       <c r="S13" t="n">
-        <v>9000</v>
+        <v>13000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차', 'LNG']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213500</v>
+        <v>18800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.64%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>-0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>238</v>
+        <v>567</v>
       </c>
       <c r="H14" t="n">
-        <v>75.5</v>
+        <v>10.47</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>208000</v>
+        <v>18290</v>
       </c>
       <c r="K14" t="n">
-        <v>215000</v>
+        <v>18830</v>
       </c>
       <c r="L14" t="n">
-        <v>215000</v>
+        <v>19540</v>
       </c>
       <c r="M14" t="n">
-        <v>211000</v>
+        <v>18540</v>
       </c>
       <c r="N14" t="n">
-        <v>75.44</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>529296318750</v>
+        <v>108088813175</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>64700</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-691000</v>
+        <v>-76000</v>
       </c>
       <c r="S14" t="n">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['공매도', '대차', 'LNG']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1916000</v>
+        <v>281250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="G15" t="n">
-        <v>2394</v>
+        <v>2045</v>
       </c>
       <c r="H15" t="n">
-        <v>50.17</v>
+        <v>46.56</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1868000</v>
+        <v>274000</v>
       </c>
       <c r="K15" t="n">
-        <v>1909000</v>
+        <v>283000</v>
       </c>
       <c r="L15" t="n">
-        <v>1935000</v>
+        <v>283500</v>
       </c>
       <c r="M15" t="n">
-        <v>1904000</v>
+        <v>278500</v>
       </c>
       <c r="N15" t="n">
-        <v>50.23</v>
+        <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>2699607848500</v>
+        <v>2341073337750</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>333000</v>
+        <v>81100</v>
       </c>
       <c r="R15" t="n">
-        <v>82000</v>
+        <v>-116000</v>
       </c>
       <c r="S15" t="n">
-        <v>44000</v>
+        <v>128000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 개발 경쟁 심화 및 앤트로픽 신규 모델 출시 검토 소식에 따른 상승 기대. 200만원 돌파 및 전고점 돌파 전망.</t>
+          <t>AI 낙관론으로 인한 기대감 속 배당 기대감 존재. 단기 목표가 30만원 돌파 및 장기적으로 67만원까지 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '앤트로픽', '자사주']</t>
+          <t>['AI', '배당', '목표가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>281000</v>
+        <v>1914000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="G16" t="n">
-        <v>2079</v>
+        <v>2318</v>
       </c>
       <c r="H16" t="n">
-        <v>46.56</v>
+        <v>50.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>274000</v>
+        <v>1868000</v>
       </c>
       <c r="K16" t="n">
-        <v>283000</v>
+        <v>1909000</v>
       </c>
       <c r="L16" t="n">
-        <v>283500</v>
+        <v>1935000</v>
       </c>
       <c r="M16" t="n">
-        <v>278500</v>
+        <v>1904000</v>
       </c>
       <c r="N16" t="n">
-        <v>46.46</v>
+        <v>50.23</v>
       </c>
       <c r="O16" t="n">
-        <v>2289893383750</v>
+        <v>2753554587000</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>81100</v>
+        <v>333000</v>
       </c>
       <c r="R16" t="n">
-        <v>-116000</v>
+        <v>82000</v>
       </c>
       <c r="S16" t="n">
-        <v>128000</v>
+        <v>44000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론과 배당 기대감 속에서 30만 돌파 가능성 언급. 다만, 정치적 발언 혼재.</t>
+          <t>AI 개발 관련 긍정적 뉴스 속에서 200돌파 및 230-240까지 상승 전망. 자사주 매수 기대감 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '배당', 'HBM']</t>
+          <t>['AI', '200돌파', '자사주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13280</v>
+        <v>13260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>19722898590</v>
+        <v>19899920750</v>
       </c>
       <c r="P17" t="n">
         <v>19380</v>
@@ -2050,13 +2050,13 @@
         <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H18" t="n">
         <v>1.2</v>
@@ -2082,7 +2082,7 @@
         <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>45947383200</v>
+        <v>47607048625</v>
       </c>
       <c r="P18" t="n">
         <v>22900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10660</v>
+        <v>10690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+1.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.01</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H19" t="n">
         <v>9.609999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>119037992815</v>
+        <v>120668847080</v>
       </c>
       <c r="P19" t="n">
         <v>11640</v>
@@ -2234,13 +2234,13 @@
         <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G20" t="n">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="H20" t="n">
         <v>6.22</v>
@@ -2266,7 +2266,7 @@
         <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>138554354545</v>
+        <v>139738655935</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 기대감. 2만원 돌파 및 급등 전망.</t>
+          <t>미국 광통신주 강세에 따른 기대감. 2만원 돌파 및 상한가 갈 준비 완료 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '급등']</t>
+          <t>['광통신', '2만원', '상한가']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86000</v>
+        <v>86050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F21" t="n">
         <v>180</v>
       </c>
       <c r="G21" t="n">
-        <v>1119</v>
+        <v>1139</v>
       </c>
       <c r="H21" t="n">
         <v>23.05</v>
@@ -2358,7 +2358,7 @@
         <v>23.12</v>
       </c>
       <c r="O21" t="n">
-        <v>116316715150</v>
+        <v>117811662300</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8540</v>
+        <v>8555</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>15967936770</v>
+        <v>16264264395</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 속에서 LG디스플레이의 실적 개선 및 주가 상승에 대한 회의적 시각.</t>
+          <t>실적 부진에도 불구하고 주가 상승 기대감 언급 있으나, 적자 회사 및 구제불능이라는 부정적 평가 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '적자', '주가']</t>
+          <t>['적자', '주가', '상승']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24250</v>
+        <v>24500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.96%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H23" t="n">
         <v>1.76</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>94885665750</v>
+        <v>95537934925</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 임상 FDA 관련 기대감 속에서 단기 급등 후 하락세. 투자자들의 혼란과 탈출 시도.</t>
+          <t>미국 임상 FDA 관련 뉴스에도 불구하고, 주가 하락 및 횡보에 대한 불만 존재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['미국임상', 'FDA', '급등']</t>
+          <t>['미국임상', 'FDA', '횡보']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3865</v>
+        <v>3870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.69%</t>
+          <t>'-4.56%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2605,10 +2605,10 @@
         <v>77</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>9836390822</v>
+        <v>9878769937</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10410</v>
+        <v>10390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.06%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>55</v>
       </c>
       <c r="G25" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>35775881960</v>
+        <v>36002324540</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_12.xlsx
+++ b/data/trending_integrated_20260922_12.xlsx
@@ -578,7 +578,7 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
         <v>95</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51974111840</v>
+        <v>51978689490</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -673,10 +673,10 @@
         <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5402814829</v>
+        <v>5403455299</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65200</v>
+        <v>65750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.67%</t>
+          <t>'+25.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>155627575250</v>
+        <v>157695420850</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 공급 계약 뉴스에 따른 급등세. 고점 매도 의견과 추가 상승 기대 상존.</t>
+          <t>브로드컴 공급 계약 뉴스와 키맞추기 상승 기대. 반도체 섹터 내 강세 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['브로드컴', '공급계약', '키맞추기']</t>
+          <t>['브로드컴', '공급 계약', '반도체']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13180</v>
+        <v>13200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+18.53%</t>
+          <t>'+18.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>148973537155</v>
+        <v>152012923200</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대미 투자 1호 가스 발전 관련 뉴스에도 불구하고, 하한가 및 개잡주라는 부정적 평가 우세.</t>
+          <t>대미투자 1호 가스터빈 사업 관련 보도. 주가 급등 및 하락 논쟁.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대미투자', '가스터빈', '개잡주']</t>
+          <t>['가스터빈', '대미투자', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115200</v>
+        <v>115400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.05%</t>
+          <t>'+13.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
         <v>86</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>274776141800</v>
+        <v>275600647250</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32300</v>
+        <v>32500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.75%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>231997917825</v>
+        <v>234901690625</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30725</v>
+        <v>30750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.50%</t>
+          <t>'+6.59%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,10 +1136,10 @@
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
-        <v>51.99</v>
+        <v>52.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>87066267850</v>
+        <v>90294600550</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1222,13 +1222,13 @@
         <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>62855381985</v>
+        <v>63484223650</v>
       </c>
       <c r="P9" t="n">
         <v>13140</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>331000</v>
+        <v>332000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+4.24%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>3.62</v>
       </c>
       <c r="O10" t="n">
-        <v>106696244500</v>
+        <v>107670270500</v>
       </c>
       <c r="P10" t="n">
         <v>635000</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6550</v>
+        <v>6570</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+4.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
         <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H11" t="n">
         <v>4.86</v>
@@ -1438,7 +1438,7 @@
         <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>49289308990</v>
+        <v>49474125045</v>
       </c>
       <c r="P11" t="n">
         <v>11760</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13960</v>
+        <v>18900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+3.34%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>129</v>
+        <v>576</v>
       </c>
       <c r="H12" t="n">
-        <v>3.34</v>
+        <v>10.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13540</v>
+        <v>18290</v>
       </c>
       <c r="K12" t="n">
-        <v>13870</v>
+        <v>18830</v>
       </c>
       <c r="L12" t="n">
-        <v>14650</v>
+        <v>19540</v>
       </c>
       <c r="M12" t="n">
-        <v>13740</v>
+        <v>18540</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>10.74</v>
       </c>
       <c r="O12" t="n">
-        <v>87548516380</v>
+        <v>110350900920</v>
       </c>
       <c r="P12" t="n">
-        <v>20300</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>2885</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>18000</v>
+        <v>-76000</v>
       </c>
       <c r="S12" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['공매도', '대차', 'LNG']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>214000</v>
+        <v>214500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+3.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="H13" t="n">
         <v>75.5</v>
@@ -1622,7 +1622,7 @@
         <v>75.44</v>
       </c>
       <c r="O13" t="n">
-        <v>539294732250</v>
+        <v>556677938500</v>
       </c>
       <c r="P13" t="n">
         <v>243500</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18800</v>
+        <v>13960</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>567</v>
+        <v>129</v>
       </c>
       <c r="H14" t="n">
-        <v>10.47</v>
+        <v>3.34</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18290</v>
+        <v>13540</v>
       </c>
       <c r="K14" t="n">
-        <v>18830</v>
+        <v>13870</v>
       </c>
       <c r="L14" t="n">
-        <v>19540</v>
+        <v>14650</v>
       </c>
       <c r="M14" t="n">
-        <v>18540</v>
+        <v>13740</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>3.68</v>
       </c>
       <c r="O14" t="n">
-        <v>108088813175</v>
+        <v>87935585115</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>20300</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>2885</v>
       </c>
       <c r="R14" t="n">
-        <v>-76000</v>
+        <v>18000</v>
       </c>
       <c r="S14" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차', 'LNG']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G15" t="n">
-        <v>2045</v>
+        <v>2009</v>
       </c>
       <c r="H15" t="n">
         <v>46.56</v>
@@ -1806,7 +1806,7 @@
         <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>2341073337750</v>
+        <v>2451085264000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 낙관론으로 인한 기대감 속 배당 기대감 존재. 단기 목표가 30만원 돌파 및 장기적으로 67만원까지 기대.</t>
+          <t>AI 낙관론과 배당금 기대감에 따른 주가 상승 전망. 외인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '배당', '목표가']</t>
+          <t>['AI', '배당금', '낙관론']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1914000</v>
+        <v>13300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>481</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>2318</v>
+        <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>50.17</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1868000</v>
+        <v>12960</v>
       </c>
       <c r="K16" t="n">
-        <v>1909000</v>
+        <v>13500</v>
       </c>
       <c r="L16" t="n">
-        <v>1935000</v>
+        <v>14190</v>
       </c>
       <c r="M16" t="n">
-        <v>1904000</v>
+        <v>13250</v>
       </c>
       <c r="N16" t="n">
-        <v>50.23</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2753554587000</v>
+        <v>20052819195</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>333000</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>82000</v>
+        <v>-41000</v>
       </c>
       <c r="S16" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 개발 관련 긍정적 뉴스 속에서 200돌파 및 230-240까지 상승 전망. 자사주 매수 기대감 존재.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '200돌파', '자사주']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13260</v>
+        <v>1913500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.31%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>480</v>
       </c>
       <c r="G17" t="n">
-        <v>318</v>
+        <v>2264</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>50.17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,183 +1975,183 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12960</v>
+        <v>1868000</v>
       </c>
       <c r="K17" t="n">
-        <v>13500</v>
+        <v>1909000</v>
       </c>
       <c r="L17" t="n">
-        <v>14190</v>
+        <v>1935000</v>
       </c>
       <c r="M17" t="n">
-        <v>13250</v>
+        <v>1904000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>50.23</v>
       </c>
       <c r="O17" t="n">
-        <v>19899920750</v>
+        <v>2804454670500</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>333000</v>
       </c>
       <c r="R17" t="n">
-        <v>-41000</v>
+        <v>82000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 산업 성장 및 자사주 매수 기대감에 따른 주가 상승 전망. 200 돌파 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI', '자사주 매수', '상승']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21850</v>
+        <v>86400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.63%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="G18" t="n">
-        <v>194</v>
+        <v>1165</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>23.05</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>21500</v>
+        <v>85300</v>
       </c>
       <c r="K18" t="n">
-        <v>21200</v>
+        <v>87000</v>
       </c>
       <c r="L18" t="n">
-        <v>22900</v>
+        <v>87000</v>
       </c>
       <c r="M18" t="n">
-        <v>20850</v>
+        <v>85200</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>23.12</v>
       </c>
       <c r="O18" t="n">
-        <v>47607048625</v>
+        <v>121993967250</v>
       </c>
       <c r="P18" t="n">
-        <v>22900</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>47000</v>
+        <v>-200000</v>
       </c>
       <c r="S18" t="n">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>대미투자 SMR 추진 확정 소식에 따른 주가 상승 기대감. 공급 계약 체결.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['SMR', '대미투자', '공급 계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10690</v>
+        <v>21750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+1.33%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="H19" t="n">
-        <v>9.609999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10550</v>
+        <v>21500</v>
       </c>
       <c r="K19" t="n">
-        <v>10730</v>
+        <v>21200</v>
       </c>
       <c r="L19" t="n">
-        <v>11160</v>
+        <v>22900</v>
       </c>
       <c r="M19" t="n">
-        <v>10300</v>
+        <v>20850</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>120668847080</v>
+        <v>48303264875</v>
       </c>
       <c r="P19" t="n">
-        <v>11640</v>
+        <v>22900</v>
       </c>
       <c r="Q19" t="n">
-        <v>3735</v>
+        <v>9900</v>
       </c>
       <c r="R19" t="n">
-        <v>209000</v>
+        <v>47000</v>
       </c>
       <c r="S19" t="n">
-        <v>-38000</v>
+        <v>-3000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17900</v>
+        <v>10670</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+1.02%</t>
+          <t>'+1.14%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.68</v>
+        <v>1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>702</v>
+        <v>173</v>
       </c>
       <c r="H20" t="n">
-        <v>6.22</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,143 +2251,143 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17720</v>
+        <v>10550</v>
       </c>
       <c r="K20" t="n">
-        <v>18230</v>
+        <v>10730</v>
       </c>
       <c r="L20" t="n">
-        <v>18750</v>
+        <v>11160</v>
       </c>
       <c r="M20" t="n">
-        <v>17500</v>
+        <v>10300</v>
       </c>
       <c r="N20" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>139738655935</v>
+        <v>122918708300</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>11640</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>3735</v>
       </c>
       <c r="R20" t="n">
-        <v>-545000</v>
+        <v>209000</v>
       </c>
       <c r="S20" t="n">
-        <v>7000</v>
+        <v>-38000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 기대감. 2만원 돌파 및 상한가 갈 준비 완료 언급.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '2만원', '상한가']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86050</v>
+        <v>17900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.68</v>
       </c>
       <c r="E21" t="n">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="F21" t="n">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="G21" t="n">
-        <v>1139</v>
+        <v>715</v>
       </c>
       <c r="H21" t="n">
-        <v>23.05</v>
+        <v>6.22</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>85300</v>
+        <v>17720</v>
       </c>
       <c r="K21" t="n">
-        <v>87000</v>
+        <v>18230</v>
       </c>
       <c r="L21" t="n">
-        <v>87000</v>
+        <v>18750</v>
       </c>
       <c r="M21" t="n">
-        <v>85200</v>
+        <v>17500</v>
       </c>
       <c r="N21" t="n">
-        <v>23.12</v>
+        <v>7.9</v>
       </c>
       <c r="O21" t="n">
-        <v>117811662300</v>
+        <v>141063499280</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>-200000</v>
+        <v>-545000</v>
       </c>
       <c r="S21" t="n">
-        <v>-4000</v>
+        <v>7000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 SMR 추진 및 가스터빈 사업 관련 확정 소식에 따른 강한 상승 기대감. 10만 돌파 및 상한가 가능성 언급.</t>
+          <t>미국 광통신주 강세에 따른 기대감. 2만원 돌파 및 상한가 갈 준비 완료 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '대미투자']</t>
+          <t>['광통신', '2만원', '상한가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8555</v>
+        <v>8560</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F22" t="n">
         <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>16264264395</v>
+        <v>16448507895</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>실적 부진에도 불구하고 주가 상승 기대감 언급 있으나, 적자 회사 및 구제불능이라는 부정적 평가 존재.</t>
+          <t>실적 개선 및 기술 혁신에 따른 장기적 가치 상승 가능성 언급. 대차잔고 감소.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['적자', '주가', '상승']</t>
+          <t>['실적', '기술 혁신', '대차잔고']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24500</v>
+        <v>24400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H23" t="n">
         <v>1.76</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>95537934925</v>
+        <v>96171656275</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3870</v>
+        <v>3860</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.56%</t>
+          <t>'-4.81%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>9878769937</v>
+        <v>9934053482</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+          <t>코인 관련주로서의 텐베거 기대감과 단기 급락 가능성 혼재. 차트 분석.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['비트코인', '차트분석', '신용물량']</t>
+          <t>['코인', '텐베거', '급락']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10390</v>
+        <v>10480</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-5.24%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>36002324540</v>
+        <v>36367863040</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
+          <t>투자경고 종목 지정 관련 부정적 전망. 차트 하락 추세.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['투자경고', '돌파', '차트']</t>
+          <t>['투자경고', '하락', '차트']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">

--- a/data/trending_integrated_20260922_12.xlsx
+++ b/data/trending_integrated_20260922_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51978689490</v>
+        <v>51981598440</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스에 따른 기대감 고조. 다만, 실적 부재 및 주가 하락 우려도 공존.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스. AI 반도체 파트너십 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5403455299</v>
+        <v>5405091094</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65750</v>
+        <v>66200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.72%</t>
+          <t>'+26.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>157695420850</v>
+        <v>158763961350</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,12 +810,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 공급 계약 뉴스와 키맞추기 상승 기대. 반도체 섹터 내 강세 전망.</t>
+          <t>브로드컴 투자 공급 계약 관련 기대감. 반도체 섹터 내 키 맞추기 움직임.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13200</v>
+        <v>12920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+18.71%</t>
+          <t>'+16.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>152012923200</v>
+        <v>158281628980</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대미투자 1호 가스터빈 사업 관련 보도. 주가 급등 및 하락 논쟁.</t>
+          <t>대미 투자 및 가스터빈 관련 뉴스 언급되나, 급락 및 개잡주 평가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '대미투자', '급등']</t>
+          <t>['대미 투자', '가스터빈', '개잡주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115400</v>
+        <v>115000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.25%</t>
+          <t>'+12.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>275600647250</v>
+        <v>276677548650</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32500</v>
+        <v>32450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+9.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>234901690625</v>
+        <v>239284240525</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속에서 주가 상승 기대감 있으나, 전고점 돌파 실패 및 외인/기관 매도 시작으로 부정적.</t>
+          <t>AI 전력 수요 증가 관련 기대감 속 신고점 돌파 시도. 가온전선과의 비교 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전고점', '외인', '기관']</t>
+          <t>['AI', '전력 수요', '신고점']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30750</v>
+        <v>30700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+6.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H8" t="n">
-        <v>52.01</v>
+        <v>52.03</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>90294600550</v>
+        <v>94023012425</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6140</v>
+        <v>6110</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.78%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
         <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>6110</v>
+        <v>6100</v>
       </c>
       <c r="N9" t="n">
         <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>63484223650</v>
+        <v>63988314495</v>
       </c>
       <c r="P9" t="n">
         <v>13140</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>비트코인 급등에 따른 코인주 반란 기대감. 업비트 나스닥 상장 및 비트코인 신고가 경신 가능성 언급.</t>
+          <t>비트코인 급등에 따른 코인 테마주 반등 기대. 업비트 상장 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['비트코인', '코인주', '공매도']</t>
+          <t>['비트코인', '코인 테마', '업비트']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>332000</v>
+        <v>6560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>264</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>318500</v>
+        <v>6310</v>
       </c>
       <c r="K10" t="n">
-        <v>333000</v>
+        <v>6460</v>
       </c>
       <c r="L10" t="n">
-        <v>349500</v>
+        <v>7090</v>
       </c>
       <c r="M10" t="n">
-        <v>325000</v>
+        <v>6350</v>
       </c>
       <c r="N10" t="n">
-        <v>3.62</v>
+        <v>4.95</v>
       </c>
       <c r="O10" t="n">
-        <v>107670270500</v>
+        <v>49618966175</v>
       </c>
       <c r="P10" t="n">
-        <v>635000</v>
+        <v>11760</v>
       </c>
       <c r="Q10" t="n">
-        <v>52600</v>
+        <v>1620</v>
       </c>
       <c r="R10" t="n">
-        <v>-8000</v>
+        <v>-92000</v>
       </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['신고가', '테마주', '외인지분율']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,91 +1379,91 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6570</v>
+        <v>331000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.12%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="H11" t="n">
-        <v>4.86</v>
+        <v>3.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6310</v>
+        <v>318500</v>
       </c>
       <c r="K11" t="n">
-        <v>6460</v>
+        <v>333000</v>
       </c>
       <c r="L11" t="n">
-        <v>7090</v>
+        <v>349500</v>
       </c>
       <c r="M11" t="n">
-        <v>6350</v>
+        <v>325000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.95</v>
+        <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>49474125045</v>
+        <v>108252227500</v>
       </c>
       <c r="P11" t="n">
-        <v>11760</v>
+        <v>635000</v>
       </c>
       <c r="Q11" t="n">
-        <v>1620</v>
+        <v>52600</v>
       </c>
       <c r="R11" t="n">
-        <v>-92000</v>
+        <v>-8000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>신고가 경신 및 52주 신고가 돌파 기대감. 모더나, 텍사스 가스복합발전 프로젝트 테마 연관성 언급. 외인 지분율 상승.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['신고가', '테마주', '외인지분율']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18900</v>
+        <v>18990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.34%</t>
+          <t>'+3.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="H12" t="n">
         <v>10.47</v>
@@ -1530,7 +1530,7 @@
         <v>10.74</v>
       </c>
       <c r="O12" t="n">
-        <v>110350900920</v>
+        <v>112024524670</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>공매도 세력과의 전쟁 및 대차 해지 촉구. LNG, 원전 등 신규 사업 기대감 언급.</t>
+          <t>공매도 세력과의 갈등 및 주가 조작 의혹 제기. 연기금 투입 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '대차', 'LNG']</t>
+          <t>['공매도', '시세조종', '연기금']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>214500</v>
+        <v>215000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.12%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="H13" t="n">
         <v>75.5</v>
@@ -1622,7 +1622,7 @@
         <v>75.44</v>
       </c>
       <c r="O13" t="n">
-        <v>556677938500</v>
+        <v>586053258000</v>
       </c>
       <c r="P13" t="n">
         <v>243500</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13960</v>
+        <v>13980</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+3.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="H14" t="n">
         <v>3.34</v>
@@ -1714,7 +1714,7 @@
         <v>3.68</v>
       </c>
       <c r="O14" t="n">
-        <v>87935585115</v>
+        <v>88194078275</v>
       </c>
       <c r="P14" t="n">
         <v>20300</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>281250</v>
+        <v>13340</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>493</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>2009</v>
+        <v>322</v>
       </c>
       <c r="H15" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>274000</v>
+        <v>12960</v>
       </c>
       <c r="K15" t="n">
-        <v>283000</v>
+        <v>13500</v>
       </c>
       <c r="L15" t="n">
-        <v>283500</v>
+        <v>14190</v>
       </c>
       <c r="M15" t="n">
-        <v>278500</v>
+        <v>13250</v>
       </c>
       <c r="N15" t="n">
-        <v>46.46</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2451085264000</v>
+        <v>20218055595</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>81100</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-116000</v>
+        <v>-41000</v>
       </c>
       <c r="S15" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 낙관론과 배당금 기대감에 따른 주가 상승 전망. 외인/기관 매수세 유입.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '배당금', '낙관론']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13300</v>
+        <v>281500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.74%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>494</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>2055</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12960</v>
+        <v>274000</v>
       </c>
       <c r="K16" t="n">
-        <v>13500</v>
+        <v>283000</v>
       </c>
       <c r="L16" t="n">
-        <v>14190</v>
+        <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>13250</v>
+        <v>278500</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>20052819195</v>
+        <v>2498911607000</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>-41000</v>
+        <v>-116000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>128000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 낙관론 및 배당 기대감에 따른 주가 상승 전망. 외인·기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI', '배당금', '외인']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1913500</v>
+        <v>1909000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G17" t="n">
-        <v>2264</v>
+        <v>2232</v>
       </c>
       <c r="H17" t="n">
         <v>50.17</v>
@@ -1990,7 +1990,7 @@
         <v>50.23</v>
       </c>
       <c r="O17" t="n">
-        <v>2804454670500</v>
+        <v>2877199318500</v>
       </c>
       <c r="P17" t="n">
         <v>2987000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 산업 성장 및 자사주 매수 기대감에 따른 주가 상승 전망. 200 돌파 기대.</t>
+          <t>AI 관련주로서의 상승 기대감. 전고점 돌파 시도 및 자사주 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '자사주 매수', '상승']</t>
+          <t>['AI', '전고점', '자사주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86400</v>
+        <v>86600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.52%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F18" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G18" t="n">
-        <v>1165</v>
+        <v>1194</v>
       </c>
       <c r="H18" t="n">
         <v>23.05</v>
@@ -2082,7 +2082,7 @@
         <v>23.12</v>
       </c>
       <c r="O18" t="n">
-        <v>121993967250</v>
+        <v>125957907700</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21750</v>
+        <v>10660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>1.01</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>21500</v>
+        <v>10550</v>
       </c>
       <c r="K19" t="n">
-        <v>21200</v>
+        <v>10730</v>
       </c>
       <c r="L19" t="n">
-        <v>22900</v>
+        <v>11160</v>
       </c>
       <c r="M19" t="n">
-        <v>20850</v>
+        <v>10300</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>48303264875</v>
+        <v>124123712035</v>
       </c>
       <c r="P19" t="n">
-        <v>22900</v>
+        <v>11640</v>
       </c>
       <c r="Q19" t="n">
-        <v>9900</v>
+        <v>3735</v>
       </c>
       <c r="R19" t="n">
-        <v>47000</v>
+        <v>209000</v>
       </c>
       <c r="S19" t="n">
-        <v>-3000</v>
+        <v>-38000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10670</v>
+        <v>17900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+1.14%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="G20" t="n">
-        <v>173</v>
+        <v>733</v>
       </c>
       <c r="H20" t="n">
-        <v>9.609999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10550</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>10730</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>11160</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>10300</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>122918708300</v>
+        <v>142342888760</v>
       </c>
       <c r="P20" t="n">
-        <v>11640</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3735</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>209000</v>
+        <v>-545000</v>
       </c>
       <c r="S20" t="n">
-        <v>-38000</v>
+        <v>7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>미국 광통신 섹터 강세에 따른 기대감. 메타발 광케이블 공급 계약 가능성.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['광통신', '메타', '광케이블']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17900</v>
+        <v>21600</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+1.02%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.68</v>
+        <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>715</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
-        <v>6.22</v>
+        <v>1.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,60 +2343,60 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17720</v>
+        <v>21500</v>
       </c>
       <c r="K21" t="n">
-        <v>18230</v>
+        <v>21200</v>
       </c>
       <c r="L21" t="n">
-        <v>18750</v>
+        <v>22900</v>
       </c>
       <c r="M21" t="n">
-        <v>17500</v>
+        <v>20850</v>
       </c>
       <c r="N21" t="n">
-        <v>7.9</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>141063499280</v>
+        <v>48768776825</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>22900</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>9900</v>
       </c>
       <c r="R21" t="n">
-        <v>-545000</v>
+        <v>47000</v>
       </c>
       <c r="S21" t="n">
-        <v>7000</v>
+        <v>-3000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 기대감. 2만원 돌파 및 상한가 갈 준비 완료 언급.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '2만원', '상한가']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8560</v>
+        <v>8540</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>16448507895</v>
+        <v>16805294800</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24400</v>
+        <v>24450</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
         <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="H23" t="n">
         <v>1.76</v>
@@ -2542,7 +2542,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>96171656275</v>
+        <v>96542433425</v>
       </c>
       <c r="P23" t="n">
         <v>39350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 임상 FDA 관련 뉴스에도 불구하고, 주가 하락 및 횡보에 대한 불만 존재.</t>
+          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['미국임상', 'FDA', '횡보']</t>
+          <t>['FDA', '임상', '재무']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3860</v>
+        <v>3850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.81%</t>
+          <t>'-5.06%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F24" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G24" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H24" t="n">
         <v>0.96</v>
@@ -2634,7 +2634,7 @@
         <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>9934053482</v>
+        <v>10004938362</v>
       </c>
       <c r="P24" t="n">
         <v>6480</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10480</v>
+        <v>10400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.24%</t>
+          <t>'-5.97%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
         <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>36367863040</v>
+        <v>36884282985</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
